--- a/output_data/charts/crashSeverityByType-Fairfield.xlsx
+++ b/output_data/charts/crashSeverityByType-Fairfield.xlsx
@@ -40,31 +40,31 @@
     <t>Overturning</t>
   </si>
   <si>
+    <t>Pedestrian</t>
+  </si>
+  <si>
     <t>Left Turn</t>
   </si>
   <si>
     <t>Rear End</t>
   </si>
   <si>
-    <t>Pedestrian</t>
-  </si>
-  <si>
     <t>Sideswipe - Passing</t>
   </si>
   <si>
+    <t>Backing</t>
+  </si>
+  <si>
     <t>Other Non-Collision</t>
   </si>
   <si>
+    <t>Pedalcycles</t>
+  </si>
+  <si>
+    <t>Right Turn</t>
+  </si>
+  <si>
     <t>Sideswipe - Meeting</t>
-  </si>
-  <si>
-    <t>Right Turn</t>
-  </si>
-  <si>
-    <t>Backing</t>
-  </si>
-  <si>
-    <t>Pedalcycles</t>
   </si>
   <si>
     <t>Other Object</t>
@@ -225,31 +225,31 @@
                   <c:v>Overturning</c:v>
                 </c:pt>
                 <c:pt idx="4">
+                  <c:v>Pedestrian</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>Left Turn</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>Rear End</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>Pedestrian</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>Sideswipe - Passing</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>Backing</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>Other Non-Collision</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="10">
+                  <c:v>Pedalcycles</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Right Turn</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>Sideswipe - Meeting</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>Right Turn</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>Backing</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>Pedalcycles</c:v>
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>Other Object</c:v>
@@ -273,43 +273,43 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="17"/>
                 <c:pt idx="0">
-                  <c:v>32.87671232876712</c:v>
+                  <c:v>38.88888888888889</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>15.06849315068493</c:v>
+                  <c:v>12.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>9.58904109589041</c:v>
+                  <c:v>9.722222222222223</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>9.58904109589041</c:v>
+                  <c:v>9.722222222222223</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>9.58904109589041</c:v>
+                  <c:v>6.944444444444445</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>6.849315068493151</c:v>
+                  <c:v>5.555555555555555</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>5.47945205479452</c:v>
+                  <c:v>5.555555555555555</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>4.10958904109589</c:v>
+                  <c:v>4.166666666666666</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.36986301369863</c:v>
+                  <c:v>1.388888888888889</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.36986301369863</c:v>
+                  <c:v>1.388888888888889</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.36986301369863</c:v>
+                  <c:v>1.388888888888889</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.36986301369863</c:v>
+                  <c:v>1.388888888888889</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.36986301369863</c:v>
+                  <c:v>1.388888888888889</c:v>
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>0</c:v>
@@ -367,31 +367,31 @@
                   <c:v>Overturning</c:v>
                 </c:pt>
                 <c:pt idx="4">
+                  <c:v>Pedestrian</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>Left Turn</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>Rear End</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>Pedestrian</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>Sideswipe - Passing</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>Backing</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>Other Non-Collision</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="10">
+                  <c:v>Pedalcycles</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Right Turn</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>Sideswipe - Meeting</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>Right Turn</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>Backing</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>Pedalcycles</c:v>
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>Other Object</c:v>
@@ -415,55 +415,55 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="17"/>
                 <c:pt idx="0">
-                  <c:v>28.21782178217822</c:v>
+                  <c:v>27.62148337595908</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>8.168316831683169</c:v>
+                  <c:v>6.393861892583121</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>18.56435643564356</c:v>
+                  <c:v>19.18158567774936</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4.95049504950495</c:v>
+                  <c:v>4.092071611253197</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>8.91089108910891</c:v>
+                  <c:v>7.928388746803069</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>7.178217821782177</c:v>
+                  <c:v>9.974424552429667</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>7.673267326732673</c:v>
+                  <c:v>8.184143222506394</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>5.940594059405941</c:v>
+                  <c:v>5.626598465473146</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.485148514851485</c:v>
+                  <c:v>0.7672634271099744</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.2475247524752475</c:v>
+                  <c:v>1.278772378516624</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.9900990099009901</c:v>
+                  <c:v>2.557544757033248</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.9900990099009901</c:v>
+                  <c:v>1.278772378516624</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2.722772277227723</c:v>
+                  <c:v>0.2557544757033248</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.2475247524752475</c:v>
+                  <c:v>0.2557544757033248</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.237623762376238</c:v>
+                  <c:v>1.534526854219949</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.98019801980198</c:v>
+                  <c:v>2.813299232736573</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.495049504950495</c:v>
+                  <c:v>0.2557544757033248</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -509,31 +509,31 @@
                   <c:v>Overturning</c:v>
                 </c:pt>
                 <c:pt idx="4">
+                  <c:v>Pedestrian</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>Left Turn</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>Rear End</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>Pedestrian</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>Sideswipe - Passing</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>Backing</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>Other Non-Collision</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="10">
+                  <c:v>Pedalcycles</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Right Turn</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>Sideswipe - Meeting</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>Right Turn</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>Backing</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>Pedalcycles</c:v>
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>Other Object</c:v>
@@ -557,55 +557,55 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="17"/>
                 <c:pt idx="0">
-                  <c:v>16.99694524947129</c:v>
+                  <c:v>15.97366886092825</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.247983081381687</c:v>
+                  <c:v>2.391467377718524</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>15.32074880551422</c:v>
+                  <c:v>15.68202649779185</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.143573274849221</c:v>
+                  <c:v>0.9999166736105325</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>7.174747395629357</c:v>
+                  <c:v>0.9415882009832514</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>24.26568496906086</c:v>
+                  <c:v>7.299391717356888</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.9085924649486957</c:v>
+                  <c:v>24.08965919506708</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>11.69421163938278</c:v>
+                  <c:v>12.11565702858095</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.315892535442939</c:v>
+                  <c:v>4.816265311224065</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.03916346831675414</c:v>
+                  <c:v>1.4082159820015</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>3.375890968904206</c:v>
+                  <c:v>0.5166236146987752</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>4.895433539594266</c:v>
+                  <c:v>3.341388217648529</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.5091250881178037</c:v>
+                  <c:v>0.04166319473377219</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.2036500352471215</c:v>
+                  <c:v>0.2249812515623698</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>4.378475757813112</c:v>
+                  <c:v>4.349637530205816</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>5.177410511474896</c:v>
+                  <c:v>5.457878510124156</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.3524712148507872</c:v>
+                  <c:v>0.3499708357636864</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1061,13 +1061,13 @@
         <v>4</v>
       </c>
       <c r="B2" s="2">
-        <v>32.87671232876712</v>
+        <v>38.88888888888889</v>
       </c>
       <c r="C2" s="2">
-        <v>28.21782178217822</v>
+        <v>27.62148337595908</v>
       </c>
       <c r="D2" s="2">
-        <v>16.99694524947129</v>
+        <v>15.97366886092825</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1075,13 +1075,13 @@
         <v>5</v>
       </c>
       <c r="B3" s="2">
-        <v>15.06849315068493</v>
+        <v>12.5</v>
       </c>
       <c r="C3" s="2">
-        <v>8.168316831683169</v>
+        <v>6.393861892583121</v>
       </c>
       <c r="D3" s="2">
-        <v>2.247983081381687</v>
+        <v>2.391467377718524</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1089,13 +1089,13 @@
         <v>6</v>
       </c>
       <c r="B4" s="2">
-        <v>9.58904109589041</v>
+        <v>9.722222222222223</v>
       </c>
       <c r="C4" s="2">
-        <v>18.56435643564356</v>
+        <v>19.18158567774936</v>
       </c>
       <c r="D4" s="2">
-        <v>15.32074880551422</v>
+        <v>15.68202649779185</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1103,13 +1103,13 @@
         <v>7</v>
       </c>
       <c r="B5" s="2">
-        <v>9.58904109589041</v>
+        <v>9.722222222222223</v>
       </c>
       <c r="C5" s="2">
-        <v>4.95049504950495</v>
+        <v>4.092071611253197</v>
       </c>
       <c r="D5" s="2">
-        <v>1.143573274849221</v>
+        <v>0.9999166736105325</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1117,13 +1117,13 @@
         <v>8</v>
       </c>
       <c r="B6" s="2">
-        <v>9.58904109589041</v>
+        <v>6.944444444444445</v>
       </c>
       <c r="C6" s="2">
-        <v>8.91089108910891</v>
+        <v>7.928388746803069</v>
       </c>
       <c r="D6" s="2">
-        <v>7.174747395629357</v>
+        <v>0.9415882009832514</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1131,13 +1131,13 @@
         <v>9</v>
       </c>
       <c r="B7" s="2">
-        <v>6.849315068493151</v>
+        <v>5.555555555555555</v>
       </c>
       <c r="C7" s="2">
-        <v>7.178217821782177</v>
+        <v>9.974424552429667</v>
       </c>
       <c r="D7" s="2">
-        <v>24.26568496906086</v>
+        <v>7.299391717356888</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1145,13 +1145,13 @@
         <v>10</v>
       </c>
       <c r="B8" s="2">
-        <v>5.47945205479452</v>
+        <v>5.555555555555555</v>
       </c>
       <c r="C8" s="2">
-        <v>7.673267326732673</v>
+        <v>8.184143222506394</v>
       </c>
       <c r="D8" s="2">
-        <v>0.9085924649486957</v>
+        <v>24.08965919506708</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1159,13 +1159,13 @@
         <v>11</v>
       </c>
       <c r="B9" s="2">
-        <v>4.10958904109589</v>
+        <v>4.166666666666666</v>
       </c>
       <c r="C9" s="2">
-        <v>5.940594059405941</v>
+        <v>5.626598465473146</v>
       </c>
       <c r="D9" s="2">
-        <v>11.69421163938278</v>
+        <v>12.11565702858095</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1173,13 +1173,13 @@
         <v>12</v>
       </c>
       <c r="B10" s="2">
-        <v>1.36986301369863</v>
+        <v>1.388888888888889</v>
       </c>
       <c r="C10" s="2">
-        <v>1.485148514851485</v>
+        <v>0.7672634271099744</v>
       </c>
       <c r="D10" s="2">
-        <v>1.315892535442939</v>
+        <v>4.816265311224065</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1187,13 +1187,13 @@
         <v>13</v>
       </c>
       <c r="B11" s="2">
-        <v>1.36986301369863</v>
+        <v>1.388888888888889</v>
       </c>
       <c r="C11" s="2">
-        <v>0.2475247524752475</v>
+        <v>1.278772378516624</v>
       </c>
       <c r="D11" s="2">
-        <v>0.03916346831675414</v>
+        <v>1.4082159820015</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1201,13 +1201,13 @@
         <v>14</v>
       </c>
       <c r="B12" s="2">
-        <v>1.36986301369863</v>
+        <v>1.388888888888889</v>
       </c>
       <c r="C12" s="2">
-        <v>0.9900990099009901</v>
+        <v>2.557544757033248</v>
       </c>
       <c r="D12" s="2">
-        <v>3.375890968904206</v>
+        <v>0.5166236146987752</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1215,13 +1215,13 @@
         <v>15</v>
       </c>
       <c r="B13" s="2">
-        <v>1.36986301369863</v>
+        <v>1.388888888888889</v>
       </c>
       <c r="C13" s="2">
-        <v>0.9900990099009901</v>
+        <v>1.278772378516624</v>
       </c>
       <c r="D13" s="2">
-        <v>4.895433539594266</v>
+        <v>3.341388217648529</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1229,13 +1229,13 @@
         <v>16</v>
       </c>
       <c r="B14" s="2">
-        <v>1.36986301369863</v>
+        <v>1.388888888888889</v>
       </c>
       <c r="C14" s="2">
-        <v>2.722772277227723</v>
+        <v>0.2557544757033248</v>
       </c>
       <c r="D14" s="2">
-        <v>0.5091250881178037</v>
+        <v>0.04166319473377219</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1246,10 +1246,10 @@
         <v>0</v>
       </c>
       <c r="C15" s="2">
-        <v>0.2475247524752475</v>
+        <v>0.2557544757033248</v>
       </c>
       <c r="D15" s="2">
-        <v>0.2036500352471215</v>
+        <v>0.2249812515623698</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -1260,10 +1260,10 @@
         <v>0</v>
       </c>
       <c r="C16" s="2">
-        <v>1.237623762376238</v>
+        <v>1.534526854219949</v>
       </c>
       <c r="D16" s="2">
-        <v>4.378475757813112</v>
+        <v>4.349637530205816</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -1274,10 +1274,10 @@
         <v>0</v>
       </c>
       <c r="C17" s="2">
-        <v>1.98019801980198</v>
+        <v>2.813299232736573</v>
       </c>
       <c r="D17" s="2">
-        <v>5.177410511474896</v>
+        <v>5.457878510124156</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -1288,10 +1288,10 @@
         <v>0</v>
       </c>
       <c r="C18" s="2">
-        <v>0.495049504950495</v>
+        <v>0.2557544757033248</v>
       </c>
       <c r="D18" s="2">
-        <v>0.3524712148507872</v>
+        <v>0.3499708357636864</v>
       </c>
     </row>
   </sheetData>

--- a/output_data/charts/crashSeverityByType-Fairfield.xlsx
+++ b/output_data/charts/crashSeverityByType-Fairfield.xlsx
@@ -83,8 +83,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode=""/>
+    <numFmt numFmtId="165" formatCode="0.00"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -141,7 +142,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -173,7 +174,7 @@
               <a:rPr lang="en-US" sz="1400" baseline="0">
                 <a:latin typeface="Arial"/>
               </a:rPr>
-              <a:t>Crash Severity by Type of Crash - Fairfield County</a:t>
+              <a:t>Crash Severity by Type of Crash, Fairfield County, 2020-2024</a:t>
             </a:r>
           </a:p>
         </c:rich>
